--- a/data/dataset_table/patient_characteristics_table.xlsx
+++ b/data/dataset_table/patient_characteristics_table.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -736,154 +736,126 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unknown</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>IDH</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>IDH</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mutated</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>103 (53%)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>10 (10%)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>83 (100%)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>5 (20%)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>3 (33%)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>140 (60%)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>344 (53%)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Mutated</t>
+          <t xml:space="preserve">  Wildtype</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>103 (53%)</t>
+          <t>90 (47%)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>10 (10%)</t>
+          <t>93 (90%)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>83 (100%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>5 (20%)</t>
+          <t>20 (80%)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>3 (33%)</t>
+          <t>6 (67%)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>140 (60%)</t>
+          <t>95 (40%)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>344 (53%)</t>
+          <t>304 (47%)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wildtype</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>90 (47%)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>93 (90%)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>20 (80%)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>6 (67%)</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>95 (40%)</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>304 (47%)</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>1p/19q</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unknown</t>
+          <t xml:space="preserve">  Co-deleted</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>15 (8%)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -893,7 +865,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>27 (33%)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -903,220 +875,248 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>1 (11%)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>69 (29%)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>112 (17%)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>1p/19q</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Intact</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>152 (79%)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0 (0%)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>56 (67%)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>23 (92%)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>6 (67%)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>90 (38%)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>327 (50%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Co-deleted</t>
+          <t xml:space="preserve">  Unknown</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>15 (8%)</t>
+          <t>26 (13%)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>103 (100%)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>27 (33%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>2 (8%)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>1 (11%)</t>
+          <t>2 (22%)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>69 (29%)</t>
+          <t>76 (32%)</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>112 (17%)</t>
+          <t>209 (32%)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Intact</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>152 (79%)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>56 (67%)</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>23 (92%)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>6 (67%)</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>90 (38%)</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>327 (50%)</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Molecular Subtype</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unknown</t>
+          <t xml:space="preserve">  Oligodendroglioma</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>26 (13%)</t>
+          <t>13 (7%)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>103 (100%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>27 (33%)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2 (8%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>2 (22%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>76 (32%)</t>
+          <t>69 (29%)</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>209 (32%)</t>
+          <t>109 (17%)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Molecular Subtype</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IDH-mutant astrocytoma</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>62 (32%)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0 (0%)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>56 (67%)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0 (0%)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>1 (11%)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>66 (28%)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>185 (29%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oligodendroglioma</t>
+          <t xml:space="preserve">  Grade 4 IDH-mutant astrocytoma</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>13 (7%)</t>
+          <t>28 (15%)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>10 (10%)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>27 (33%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>5 (20%)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>2 (22%)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>69 (29%)</t>
+          <t>5 (2%)</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>109 (17%)</t>
+          <t>50 (8%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IDH-mutant astrocytoma</t>
+          <t xml:space="preserve">  IDH-wildtype glioblastoma</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1126,86 +1126,58 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>10 (10%)</t>
+          <t>93 (90%)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>56 (67%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>5 (20%)</t>
+          <t>20 (80%)</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>3 (33%)</t>
+          <t>6 (67%)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>71 (30%)</t>
+          <t>95 (40%)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>235 (36%)</t>
+          <t>304 (47%)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  IDH-wildtype glioblastoma</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>90 (47%)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>93 (90%)</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>20 (80%)</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>6 (67%)</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>95 (40%)</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>304 (47%)</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Tumor Grade</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unknown</t>
+          <t xml:space="preserve">  WHO grade 2</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>46 (24%)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1215,7 +1187,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>42 (51%)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1230,159 +1202,159 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>110 (47%)</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>198 (31%)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Tumor Grade</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHO grade 3</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>29 (15%)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0 (0%)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>41 (49%)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0 (0%)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1 (11%)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>25 (11%)</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>96 (15%)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHO grade 2</t>
+          <t xml:space="preserve">  WHO grade 4</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>46 (24%)</t>
+          <t>118 (61%)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>103 (100%)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>42 (51%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>25 (100%)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>8 (89%)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>110 (47%)</t>
+          <t>100 (43%)</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>198 (31%)</t>
+          <t>354 (55%)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHO grade 3</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>29 (15%)</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>41 (49%)</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>1 (11%)</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>25 (11%)</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>96 (15%)</t>
-        </is>
-      </c>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Multi-class Segmentation</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHO grade 4</t>
+          <t xml:space="preserve">  Manual</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>118 (61%)</t>
+          <t>193 (100%)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>103 (100%)</t>
+          <t>94 (91%)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>52 (63%)</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>25 (100%)</t>
+          <t>22 (88%)</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>8 (89%)</t>
+          <t>6 (67%)</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>100 (43%)</t>
+          <t>0 (0%)</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>354 (55%)</t>
+          <t>367 (57%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unknown</t>
+          <t xml:space="preserve">  Automatic</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1392,177 +1364,37 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>9 (9%)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>31 (37%)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>3 (12%)</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>3 (33%)</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
+          <t>235 (100%)</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Multi-class Segmentation</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Manual</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>193 (100%)</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>94 (91%)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>52 (63%)</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>22 (88%)</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>6 (67%)</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>367 (57%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Automatic</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>9 (9%)</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>31 (37%)</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>3 (12%)</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>3 (33%)</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>235 (100%)</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
           <t>281 (43%)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unknown</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>0 (0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Values are N (%), except Age which is reported as mean ± SD. Cohort defined by the unique Subject IDs in aku_annotations_with_duplicates.xlsx; subjects listed in subjects_to_discard.txt are excluded. Metadata is sourced from master_file.xlsx, joined via the AKU Center ID.</t>
         </is>
@@ -1570,7 +1402,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/dataset_table/patient_characteristics_table.xlsx
+++ b/data/dataset_table/patient_characteristics_table.xlsx
@@ -493,7 +493,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 1. Patient Characteristics Table (N = 648)</t>
+          <t>Table 1. Patient Characteristics Table (N = 646)</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>UCSF-PDGM (n=193)</t>
+          <t>UCSF-PDGM (n=191)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>TOTAL (n=648)</t>
+          <t>TOTAL (n=646)</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>49.3 ± 16.0</t>
+          <t>49.2 ± 16.0</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>70 (36%)</t>
+          <t>70 (37%)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>123 (64%)</t>
+          <t>121 (63%)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>383 (59%)</t>
+          <t>381 (59%)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>103 (53%)</t>
+          <t>103 (54%)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>90 (47%)</t>
+          <t>88 (46%)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>304 (47%)</t>
+          <t>302 (47%)</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>152 (79%)</t>
+          <t>151 (79%)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>327 (50%)</t>
+          <t>326 (50%)</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>26 (13%)</t>
+          <t>25 (13%)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>209 (32%)</t>
+          <t>208 (32%)</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>90 (47%)</t>
+          <t>88 (46%)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>304 (47%)</t>
+          <t>302 (47%)</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>118 (61%)</t>
+          <t>116 (61%)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>354 (55%)</t>
+          <t>352 (54%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>193 (100%)</t>
+          <t>191 (100%)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>367 (57%)</t>
+          <t>365 (57%)</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Values are N (%), except Age which is reported as mean ± SD. Cohort defined by the unique Subject IDs in aku_annotations_with_duplicates.xlsx; subjects listed in subjects_to_discard.txt are excluded. Metadata is sourced from master_file.xlsx, joined via the AKU Center ID.</t>
+          <t>Values are N (%), except Age which is reported as mean ± SD. Cohort defined by the unique Subject IDs in AKU_Data_by_Observer_CenterID.xlsx (Single Annotations + Duplicates sheets); subjects listed in subjects_to_discard.txt are excluded. Metadata is sourced from master_file.xlsx, joined via the AKU Center ID.</t>
         </is>
       </c>
     </row>
